--- a/03_Group_comparisons/Muscle_size/c_data/03_set_contrasts.xlsx
+++ b/03_Group_comparisons/Muscle_size/c_data/03_set_contrasts.xlsx
@@ -269,25 +269,25 @@
     <t>Where the package came from.</t>
   </si>
   <si>
-    <t>Baseline_HivLo</t>
-  </si>
-  <si>
-    <t>Training_Hi</t>
-  </si>
-  <si>
-    <t>Training_Lo</t>
-  </si>
-  <si>
-    <t>Acute_Hi</t>
-  </si>
-  <si>
-    <t>Acute_Lo</t>
-  </si>
-  <si>
-    <t>Trained_HivLo</t>
-  </si>
-  <si>
-    <t>Acute_HivLo</t>
+    <t>Baseline_HRvLR</t>
+  </si>
+  <si>
+    <t>Training_HR</t>
+  </si>
+  <si>
+    <t>Training_LR</t>
+  </si>
+  <si>
+    <t>Acute_HR</t>
+  </si>
+  <si>
+    <t>Acute_LR</t>
+  </si>
+  <si>
+    <t>Trained_HRvLR</t>
+  </si>
+  <si>
+    <t>Acute_HRvLR</t>
   </si>
   <si>
     <t>Training_Interaction</t>
@@ -8360,7 +8360,7 @@
     <t>03_Group_comparisons/Muscle_size/c_data/02_fit.rds</t>
   </si>
   <si>
-    <t>34bec5d571c34586ff8965599ef68697</t>
+    <t>97304d26b66df44dfe879e9140989a72</t>
   </si>
   <si>
     <t>design</t>
@@ -8369,13 +8369,13 @@
     <t>03_Group_comparisons/Muscle_size/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>c4dd3f50a2d661a4b677d8502617baaf</t>
+    <t>5894e9729dee108bb510385b181d74ab</t>
   </si>
   <si>
     <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
   </si>
   <si>
-    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
+    <t>015331bb453caea36bcabbe182b7eac6</t>
   </si>
   <si>
     <t>singscore</t>
@@ -8393,7 +8393,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
